--- a/GATEWAY/A1#111#ESHARKSRLXX/e-Shark S.r.l/FaithG/2.9.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#ESHARKSRLXX/e-Shark S.r.l/FaithG/2.9.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\it-fse-accreditamento\GATEWAY\A1#111#ESHARKSRLXX\e-Shark S.r.l\FaithG\2.9.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412BE35E-1839-442E-8BFA-5C1B6746ED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC815E3C-5BEF-4B8C-96C9-EBF83A5BEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="47325" yWindow="3195" windowWidth="28950" windowHeight="17550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1718,9 +1718,6 @@
 *) Il test in questione è da intendersi obbligatorio per gli applicativi che si stanno accreditando per la prima volta per PSS; nel caso di applicativi già accreditati, sarà sufficiente sottomettere il caso di test 478 (Fast Track)</t>
   </si>
   <si>
-    <t>subject_application_id:FaithK</t>
-  </si>
-  <si>
     <t>subject_application_vendor:e-Shark S.r.l.</t>
   </si>
   <si>
@@ -1746,6 +1743,9 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.190.4.4.e0c9ea2805a9ad347f05abf9081e2f64c1af5a36c35c82d34dcb03959e80e723.ce4600c1db^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>subject_application_id:FaithG</t>
   </si>
 </sst>
 </file>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="58" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D3" s="50"/>
       <c r="F3" s="6"/>
@@ -3914,7 +3914,7 @@
       <c r="A4" s="54"/>
       <c r="B4" s="55"/>
       <c r="C4" s="58" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D4" s="50"/>
       <c r="E4" s="4"/>
@@ -3941,7 +3941,7 @@
       <c r="A5" s="56"/>
       <c r="B5" s="57"/>
       <c r="C5" s="58" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D5" s="50"/>
       <c r="F5" s="6"/>
@@ -4849,7 +4849,7 @@
         <v>64</v>
       </c>
       <c r="O29" s="38" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P29" s="38" t="s">
         <v>226</v>
@@ -4861,7 +4861,7 @@
         <v>64</v>
       </c>
       <c r="S29" s="38" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="T29" s="38"/>
       <c r="U29" s="39" t="s">
@@ -10923,13 +10923,13 @@
         <v>46089</v>
       </c>
       <c r="G191" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="H191" s="37" t="s">
+        <v>445</v>
+      </c>
+      <c r="I191" s="42" t="s">
         <v>447</v>
-      </c>
-      <c r="H191" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="I191" s="42" t="s">
-        <v>448</v>
       </c>
       <c r="J191" s="38" t="s">
         <v>64</v>
@@ -10977,7 +10977,7 @@
         <v>235</v>
       </c>
       <c r="L192" s="38" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M192" s="38"/>
       <c r="N192" s="38"/>
@@ -11020,7 +11020,7 @@
         <v>235</v>
       </c>
       <c r="L193" s="38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M193" s="7"/>
       <c r="N193" s="38"/>
@@ -17272,9 +17272,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17422,27 +17425,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17466,9 +17457,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
